--- a/data/trans_orig/P13A_1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_2023-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>706</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>706</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38971</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>52800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>58202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51875</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>51875</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51875</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44485</t>
+          <t>46324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52412</t>
+          <t>54202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>63375</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55263</t>
+          <t>57945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63141</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53863</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53863</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53863</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>141532</t>
+          <t>152942</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136257</t>
+          <t>146706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144711</t>
+          <t>156686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>178926</t>
+          <t>192850</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>173133</t>
+          <t>187143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182216</t>
+          <t>196405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>147311</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147311</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>147311</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>184705</t>
+          <t>199672</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>184705</t>
+          <t>199672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>184705</t>
+          <t>199672</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
